--- a/SGC-CKN/Excel/8524d4e6-eea9-467b-8c8f-8dddea9836f3_Cọc_khoan_nhồi_P11-126_D800_06-04-2026.xlsx
+++ b/SGC-CKN/Excel/8524d4e6-eea9-467b-8c8f-8dddea9836f3_Cọc_khoan_nhồi_P11-126_D800_06-04-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="65">
   <si>
     <t>Dự án</t>
   </si>
@@ -95,13 +95,15 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét pha, xám nâu, TT dẻo mềm</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>18:20</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:10
+05/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:20
+05/04/2026</t>
   </si>
   <si>
     <t/>
@@ -110,58 +112,75 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
-  </si>
-  <si>
-    <t>19:00</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:00
+05/04/2026</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>Sét-đôi chỗ kép cát pha, lẫn dăm sạn TT dẻo mềm</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:00</t>
+    <t>Sét, đôi chỗ kẹp cát pha, lẫn dăm sạn, TT dẻo mềm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03:00
+06/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04:00
+06/04/2026</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
-  </si>
-  <si>
-    <t>04:50</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04:50
+06/04/2026</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
-  </si>
-  <si>
-    <t>06:00</t>
+    <t>Sét pha - cát pha màu xám xanh, xám ghi, lẫn hữu cơ màu xám đen, trạng thái dẻo mềm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06:00
+06/04/2026</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>07:30</t>
+    <t>Cát pha , xám vàng , xám ghi TT dẻo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:00
+06/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:30
+06/04/2026</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08:30
+06/04/2026</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t>08:30</t>
@@ -204,7 +223,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -270,6 +289,11 @@
       <name val="Arial"/>
     </font>
     <font>
+      <color rgb="FF164E63"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
@@ -282,7 +306,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -341,12 +365,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFA5F3FC"/>
       </patternFill>
     </fill>
     <fill>
@@ -442,7 +471,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -513,25 +542,34 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -557,7 +595,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8096250" cy="10477500"/>
@@ -917,7 +955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1117,10 +1155,10 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-3.13</v>
+        <v>-2.42</v>
       </c>
       <c r="H11" s="5">
         <v>0.17</v>
@@ -1152,10 +1190,10 @@
         <v>33</v>
       </c>
       <c r="F12" s="9">
-        <v>-3.13</v>
+        <v>-2.42</v>
       </c>
       <c r="G12" s="9">
-        <v>-13.33</v>
+        <v>-12.62</v>
       </c>
       <c r="H12" s="9">
         <v>0.67</v>
@@ -1187,10 +1225,10 @@
         <v>37</v>
       </c>
       <c r="F13" s="12">
-        <v>-13.33</v>
+        <v>-12.62</v>
       </c>
       <c r="G13" s="12">
-        <v>-18.53</v>
+        <v>-17.82</v>
       </c>
       <c r="H13" s="12">
         <v>1</v>
@@ -1222,10 +1260,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="15">
-        <v>-18.53</v>
+        <v>-17.82</v>
       </c>
       <c r="G14" s="15">
-        <v>-29.23</v>
+        <v>-28.52</v>
       </c>
       <c r="H14" s="15">
         <v>0.83</v>
@@ -1257,19 +1295,19 @@
         <v>43</v>
       </c>
       <c r="F15" s="18">
-        <v>-29.23</v>
+        <v>-28.52</v>
       </c>
       <c r="G15" s="18">
-        <v>-36.03</v>
+        <v>-34.4</v>
       </c>
       <c r="H15" s="18">
         <v>1.17</v>
       </c>
       <c r="I15" s="18">
-        <v>6.8</v>
+        <v>5.88</v>
       </c>
       <c r="J15" s="8">
-        <v>5.83</v>
+        <v>5.04</v>
       </c>
       <c r="K15" s="19" t="s">
         <v>30</v>
@@ -1292,75 +1330,109 @@
         <v>47</v>
       </c>
       <c r="F16" s="21">
-        <v>-36.03</v>
+        <v>-34.4</v>
       </c>
       <c r="G16" s="21">
-        <v>-46.21</v>
+        <v>-35.32</v>
       </c>
       <c r="H16" s="21">
         <v>0.5</v>
       </c>
       <c r="I16" s="21">
-        <v>10.18</v>
-      </c>
-      <c r="J16" s="8">
-        <v>20.36</v>
+        <v>0.92</v>
+      </c>
+      <c r="J16" s="24">
+        <v>1.84</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="26" t="s">
+      <c r="F17" s="25">
+        <v>-35.32</v>
+      </c>
+      <c r="G17" s="25">
+        <v>-45.5</v>
+      </c>
+      <c r="H17" s="25">
+        <v>1</v>
+      </c>
+      <c r="I17" s="25">
+        <v>10.18</v>
+      </c>
+      <c r="J17" s="8">
+        <v>10.18</v>
+      </c>
+      <c r="K17" s="26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="24">
-        <v>-46.21</v>
-      </c>
-      <c r="G17" s="24">
-        <v>-50.52</v>
-      </c>
-      <c r="H17" s="24">
+      <c r="B18" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="28">
+        <v>-45.5</v>
+      </c>
+      <c r="G18" s="28">
+        <v>-49.81</v>
+      </c>
+      <c r="H18" s="28">
         <v>1.13</v>
       </c>
-      <c r="I17" s="24">
+      <c r="I18" s="28">
         <v>4.31</v>
       </c>
-      <c r="J17" s="27">
+      <c r="J18" s="24">
         <v>3.8</v>
       </c>
-      <c r="K17" s="25" t="s">
+      <c r="K18" s="29" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-    </row>
-    <row r="21" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+    </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1420,6 +1492,7 @@
     <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="B1:K1"/>
@@ -1430,7 +1503,7 @@
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B8:K8"/>
-    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="A21:K21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1440,7 +1513,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1453,31 +1526,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1494,10 +1567,10 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-3.13</v>
+        <v>-2.42</v>
       </c>
       <c r="G2" s="5">
         <v>0.17</v>
@@ -1523,10 +1596,10 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-3.13</v>
+        <v>-2.42</v>
       </c>
       <c r="F3" s="9">
-        <v>-13.33</v>
+        <v>-12.62</v>
       </c>
       <c r="G3" s="9">
         <v>0.67</v>
@@ -1552,10 +1625,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="12">
-        <v>-13.33</v>
+        <v>-12.62</v>
       </c>
       <c r="F4" s="12">
-        <v>-18.53</v>
+        <v>-17.82</v>
       </c>
       <c r="G4" s="12">
         <v>1</v>
@@ -1581,10 +1654,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="15">
-        <v>-18.53</v>
+        <v>-17.82</v>
       </c>
       <c r="F5" s="15">
-        <v>-29.23</v>
+        <v>-28.52</v>
       </c>
       <c r="G5" s="15">
         <v>0.83</v>
@@ -1610,19 +1683,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="18">
-        <v>-29.23</v>
+        <v>-28.52</v>
       </c>
       <c r="F6" s="18">
-        <v>-36.03</v>
+        <v>-34.4</v>
       </c>
       <c r="G6" s="18">
         <v>1.17</v>
       </c>
       <c r="H6" s="18">
-        <v>6.8</v>
+        <v>5.88</v>
       </c>
       <c r="I6" s="8">
-        <v>5.83</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1639,77 +1712,106 @@
         <v>1</v>
       </c>
       <c r="E7" s="21">
-        <v>-36.03</v>
+        <v>-34.4</v>
       </c>
       <c r="F7" s="21">
-        <v>-46.21</v>
+        <v>-35.32</v>
       </c>
       <c r="G7" s="21">
         <v>0.5</v>
       </c>
       <c r="H7" s="21">
+        <v>0.92</v>
+      </c>
+      <c r="I7" s="24">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="25">
+        <v>7</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="25">
+        <v>1</v>
+      </c>
+      <c r="E8" s="25">
+        <v>-35.32</v>
+      </c>
+      <c r="F8" s="25">
+        <v>-45.5</v>
+      </c>
+      <c r="G8" s="25">
+        <v>1</v>
+      </c>
+      <c r="H8" s="25">
         <v>10.18</v>
       </c>
-      <c r="I7" s="8">
-        <v>20.36</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="24">
-        <v>7</v>
-      </c>
-      <c r="B8" s="24" t="s">
+      <c r="I8" s="8">
+        <v>10.18</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>8</v>
+      </c>
+      <c r="B9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="24">
+      <c r="C9" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="28">
         <v>1</v>
       </c>
-      <c r="E8" s="24">
-        <v>-46.21</v>
-      </c>
-      <c r="F8" s="24">
-        <v>-50.52</v>
-      </c>
-      <c r="G8" s="24">
+      <c r="E9" s="28">
+        <v>-45.5</v>
+      </c>
+      <c r="F9" s="28">
+        <v>-49.81</v>
+      </c>
+      <c r="G9" s="28">
         <v>1.13</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H9" s="28">
         <v>4.31</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I9" s="24">
         <v>3.8</v>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="30" t="s">
+    <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C10" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="30">
-        <v>7</v>
-      </c>
-      <c r="E9" s="30">
-        <v>-0.71</v>
-      </c>
-      <c r="F9" s="30">
-        <v>-50.52</v>
-      </c>
-      <c r="G9" s="30">
-        <v>5.47</v>
-      </c>
-      <c r="H9" s="30">
+      <c r="D10" s="33">
+        <v>8</v>
+      </c>
+      <c r="E10" s="33">
+        <v>0</v>
+      </c>
+      <c r="F10" s="33">
+        <v>-49.81</v>
+      </c>
+      <c r="G10" s="33">
+        <v>6.47</v>
+      </c>
+      <c r="H10" s="33">
         <v>49.81</v>
       </c>
-      <c r="I9" s="30">
-        <v>9.11</v>
+      <c r="I10" s="33">
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
